--- a/backend/src/uploads/attendance-reports/DetentionList_IT301_2026-06.xlsx
+++ b/backend/src/uploads/attendance-reports/DetentionList_IT301_2026-06.xlsx
@@ -136,7 +136,7 @@
     <t>A</t>
   </si>
   <si>
-    <t>20.00%</t>
+    <t>32.00%</t>
   </si>
 </sst>
 </file>
@@ -694,49 +694,49 @@
         <v>40</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U2" s="2" t="s">
         <v>38</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y2" s="2" t="s">
         <v>38</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AC2" s="2" t="s">
         <v>38</v>
@@ -745,19 +745,19 @@
         <v>38</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AG2" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AH2" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AI2" s="2">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="AJ2" s="3" t="s">
         <v>41</v>

--- a/backend/src/uploads/attendance-reports/DetentionList_IT301_2026-06.xlsx
+++ b/backend/src/uploads/attendance-reports/DetentionList_IT301_2026-06.xlsx
@@ -136,7 +136,7 @@
     <t>A</t>
   </si>
   <si>
-    <t>20.00%</t>
+    <t>27.27%</t>
   </si>
 </sst>
 </file>
@@ -694,7 +694,7 @@
         <v>40</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>38</v>
@@ -751,13 +751,13 @@
         <v>38</v>
       </c>
       <c r="AG2" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH2" s="2">
         <v>8</v>
       </c>
       <c r="AI2" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ2" s="3" t="s">
         <v>41</v>
